--- a/aq_files/0801.xlsx
+++ b/aq_files/0801.xlsx
@@ -1,98 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>A teacher wants to find the average marks of students in a class. Which measure of central tendency should be used?</t>
-  </si>
-  <si>
-    <t>A dataset contains extreme values (outliers), and a researcher wants a central value not affected by them. Which measure is most appropriate?</t>
-  </si>
-  <si>
-    <t>In a list of exam scores, the most frequently occurring score is identified. What measure is being used?</t>
-  </si>
-  <si>
-    <t>A company calculates the total salary of employees and divides it by the number of employees. Which measure is this?</t>
-  </si>
-  <si>
-    <t>A dataset has skewed data due to a few very high values. Which measure gives the best central value?</t>
-  </si>
-  <si>
-    <t>A researcher arranges data in ascending order and selects the middle value. What measure is this?</t>
-  </si>
-  <si>
-    <t>A shopkeeper wants to know which product is sold the most frequently. Which measure should be used?</t>
-  </si>
-  <si>
-    <t>A dataset has no repeated values. Which measure may not be meaningful in this case?</t>
-  </si>
-  <si>
-    <t>A teacher calculates the sum of marks and divides by the number of students. What measure is this?</t>
-  </si>
-  <si>
-    <t>A researcher uses the middle value of ordered data to represent the dataset. Which measure is this?</t>
-  </si>
-  <si>
-    <t>In a salary dataset where most employees earn similar wages but a few earn very high salaries, which measure is most reliable?</t>
-  </si>
-  <si>
-    <t>A dataset contains values: 2, 3, 3, 5, 7. Which measure identifies 3 as the central value based on frequency?</t>
-  </si>
-  <si>
-    <t>A researcher wants a quick measure of the central value that uses all observations. Which measure should be used?</t>
-  </si>
-  <si>
-    <t>A dataset is symmetric with no outliers. Which measure is most appropriate to represent the center?</t>
-  </si>
-  <si>
-    <t>A statistician uses a measure that may not exist if no values repeat. Which measure is this?</t>
-  </si>
-  <si>
-    <t>A researcher is analyzing household income and wants to avoid distortion from very high incomes. Which measure should be used?</t>
-  </si>
-  <si>
-    <t>A dataset has multiple values occurring with the same highest frequency. What is the situation called?</t>
-  </si>
-  <si>
-    <t>A teacher wants to know the middle score after arranging marks in order. Which measure is used?</t>
-  </si>
-  <si>
-    <t>A business analyzes the most common shoe size sold in a store. Which measure is applied?</t>
-  </si>
-  <si>
-    <t>A researcher calculates the central value by summing all values and dividing by the count. Which measure is this?</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -102,29 +38,87 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -322,113 +316,655 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="46.25" customWidth="1" style="2" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Operation</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Practical Question</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Command/Operation</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Output</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Error Scenario</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>git commit --amend</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Change the message of the most recent commit</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>git commit --amend -m "Updated commit message"</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Last commit message changed</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Only works for last commit</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>git commit --amend</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Add a forgotten file to the last commit without changing message</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>git add forgotten-file.txt, git commit --amend --no-edit</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>File added to last commit, message unchanged</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>Must have changes staged</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>git commit --amend</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Add changes and modify commit message in one operation</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>git add ., git commit --amend -m "Feature: Add login validation"</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Last commit updated with new changes and message</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Amends only last commit</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>git rebase -i</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Change commit message of a commit that is 3 commits back</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>git rebase -i HEAD~3, change "pick" to "reword" for target commit, save, edit message</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Commit message updated for specific commit</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>History rewritten, force push if pushed</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>git rebase -i</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Squash the last 3 commits into a single commit</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>git rebase -i HEAD~3, change last two "pick" to "squash", save</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>Three commits combined into one with combined message</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>May need to resolve conflicts</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>git rebase -i</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Delete a commit from history completely</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>git rebase -i HEAD~4, delete the line of the commit to remove</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>Commit removed from history</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>Data loss - careful with shared branches</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>git rebase -i</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>Reorder commits to put feature commits together</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>git rebase -i HEAD~5, reorder commit lines in editor</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>Commits in new chronological order</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>Check for dependencies between commits</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>git rebase -i</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>Split a commit into two separate commits</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>git rebase -i HEAD~1, change "pick" to "edit", git reset HEAD^, git add first-part, git commit, git add second-part, git commit, git rebase --continue</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>One commit split into two</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>Complex but powerful</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>git rebase -i</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>Fixup a commit (squash without keeping message)</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>git rebase -i HEAD~2, change "pick" to "fixup" for the commit to merge</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>Commits merged, message from first commit kept</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>Cleaner history than squash</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>git filter-branch</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>Change author name across all commits</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>git filter-branch --env-filter 'GIT_AUTHOR_NAME="New Name"' -- --all</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t>All commits author changed</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>Rewrites entire history, use with caution</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>git filter-branch</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>Change email address across entire repository</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>git filter-branch --env-filter 'GIT_AUTHOR_EMAIL="new@email.com"' -- --all</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>All commits email updated</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>Use BFG Repo-Cleaner for large repos</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>git rebase -i</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>Edit actual file content in a commit from history</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>git rebase -i HEAD~3, change "pick" to "edit", modify files, git add ., git commit --amend, git rebase --continue</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>File content changed in historical commit</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>Can cause conflicts with later commits</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>git commit --amend</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>Amend commit that was already pushed to remote</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>git commit --amend -m "New message", git push --force-with-lease origin branch</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>Remote commit updated</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>Must use force-with-lease, not --force</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>git cherry-pick</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>Apply a specific commit from another branch to current branch</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>git cherry-pick abc1234</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>Commit applied to current branch</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t>May have conflicts</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="1" t="n">
         <v>15</v>
       </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>git cherry-pick</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>Apply multiple commits from another branch with edit</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>git cherry-pick -n abc1234 def5678, git reset, git add -p, git commit</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>Multiple commits applied with customization</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>Complex conflict resolution</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>git rebase -i</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>Combine all commits on feature branch into one before merging</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>git checkout feature, git rebase -i main, squash all commits</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>Single commit representing entire feature</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>Clean main branch history</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="1" t="n">
         <v>17</v>
       </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>git commit --amend</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>Fix typo in commit message without changing content</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>git commit --amend -m "Fix: Corrected spelling in function name"</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>Commit message corrected</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>Commit hash changes</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="1" t="n">
         <v>18</v>
       </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>git rebase -i</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>Remove sensitive data (password) from specific commit</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>git rebase -i HEAD~10, edit commit, remove password, git commit --amend, git rebase --continue</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>Sensitive data removed from history</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>Use BFG for large scale removal</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="1" t="n">
         <v>19</v>
       </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>git commit --amend</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>Amend commit to change commit date</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>git commit --amend --date="2024-01-01 12:00:00" -m "Message"</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>Commit date changed</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>Useful for correcting history</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>git rebase -i</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>Reapply commits after resolving conflicts interactively</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>git rebase -i main, handle each commit with conflict resolution</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>Rebased branch with resolved conflicts</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t>Conflicts handled per commit</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>